--- a/reviews/SCFS-20260929/SCFS_Action_Plan_20261002.xlsx
+++ b/reviews/SCFS-20260929/SCFS_Action_Plan_20261002.xlsx
@@ -8,93 +8,91 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review 1 fixes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review 2 fixes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCS4 rules applied" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action list" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock &amp; reorder" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Back-up switch" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking terms" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword actions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Owner decisions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Self-competition" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword confidence" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Child economics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 Placements" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 Bid re-solve" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3k Keyword bids" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOS-first" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rank tracking" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colour costs" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Pushes" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget &amp; envelope" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New campaigns" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk upload" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs console IDs" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optional housekeeping" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Read me" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Weekly posture" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Audit review" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Campaigns" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Inventory" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Preferred variation" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Keywords" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Market" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Push test by term" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Hold test" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Rank sources" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Competitors" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Support layer" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Financials" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Placements" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E LTSF" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Conflicts" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Checks" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared rules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action list" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock &amp; reorder" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Back-up switch" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking terms" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword actions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Owner decisions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Self-competition" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword confidence" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1 Child economics" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2 Placements" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3 Bid re-solve" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3k Keyword bids" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TOS-first" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rank tracking" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colour costs" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4 Pushes" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget &amp; envelope" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New campaigns" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bulk upload" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs console IDs" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Optional housekeeping" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Read me" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Weekly posture" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Audit review" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Campaigns" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Inventory" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Preferred variation" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Keywords" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Market" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Push test by term" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Hold test" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Rank sources" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Competitors" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Support layer" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Financials" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Placements" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E LTSF" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Conflicts" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E Checks" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review 1 fixes'!$A$3:$E$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review 2 fixes'!$A$3:$E$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SCS4 rules applied'!$A$3:$D$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Action list'!$A$3:$AD$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stock &amp; reorder'!$A$3:$AB$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Back-up switch'!$A$3:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ranking terms'!$A$3:$U$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Keyword actions'!$A$3:$F$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Owner decisions'!$A$3:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Monitoring'!$A$3:$B$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Self-competition'!$A$3:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Keyword confidence'!$A$3:$I$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'T1 Child economics'!$A$3:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'T2 Placements'!$A$3:$K$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'T3 Bid re-solve'!$A$3:$AV$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'T3k Keyword bids'!$A$3:$S$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TOS-first'!$A$3:$T$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Rank tracking'!$A$3:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Colour costs'!$A$3:$O$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'T4 Pushes'!$A$3:$I$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Budget &amp; envelope'!$A$3:$F$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'New campaigns'!$A$3:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Bulk upload'!$A$3:$S$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Needs console IDs'!$A$3:$T$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Optional housekeeping'!$A$3:$F$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'E Weekly posture'!$A$3:$M$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'E Audit review'!$A$3:$K$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'E Campaigns'!$A$3:$AS$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'E Inventory'!$A$3:$AH$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'E Preferred variation'!$A$3:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'E Keywords'!$A$3:$N$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'E Market'!$A$3:$I$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'E Push test by term'!$A$3:$R$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'E Hold test'!$A$3:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'E Rank sources'!$A$3:$K$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'E Competitors'!$A$3:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'E Support layer'!$A$3:$O$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'E Financials'!$A$3:$H$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'E Placements'!$A$3:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'E LTSF'!$A$3:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'E Conflicts'!$A$3:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'E Checks'!$A$3:$C$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Key choices'!$A$3:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Shared rules'!$A$3:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Action list'!$A$3:$AD$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Stock &amp; reorder'!$A$3:$AB$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Back-up switch'!$A$3:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ranking terms'!$A$3:$U$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Keyword actions'!$A$3:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Owner decisions'!$A$3:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Monitoring'!$A$3:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Self-competition'!$A$3:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Keyword confidence'!$A$3:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'T1 Child economics'!$A$3:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'T2 Placements'!$A$3:$K$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'T3 Bid re-solve'!$A$3:$AV$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'T3k Keyword bids'!$A$3:$S$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'TOS-first'!$A$3:$T$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Rank tracking'!$A$3:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Colour costs'!$A$3:$O$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'T4 Pushes'!$A$3:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Budget &amp; envelope'!$A$3:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'New campaigns'!$A$3:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Bulk upload'!$A$3:$S$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Needs console IDs'!$A$3:$T$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Optional housekeeping'!$A$3:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'E Weekly posture'!$A$3:$M$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'E Audit review'!$A$3:$K$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'E Campaigns'!$A$3:$AS$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'E Inventory'!$A$3:$AH$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'E Preferred variation'!$A$3:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'E Keywords'!$A$3:$N$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'E Market'!$A$3:$I$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'E Push test by term'!$A$3:$R$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'E Hold test'!$A$3:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'E Rank sources'!$A$3:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'E Competitors'!$A$3:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'E Support layer'!$A$3:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'E Financials'!$A$3:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'E Placements'!$A$3:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'E LTSF'!$A$3:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'E Conflicts'!$A$3:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'E Checks'!$A$3:$C$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -566,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -576,7 +574,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sleephoria Cooling Fitted Sheet (SCFS) — action plan (2 Oct 2026, revised after review 1)</t>
+          <t>Sleephoria Cooling Fitted Sheet (SCFS) — action plan (2 Oct 2026)</t>
         </is>
       </c>
     </row>
@@ -751,36 +749,24 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Review 2</t>
+          <t>Key choices</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Five corrections and six contradictions applied (Review 2 fixes tab, with the acceptance checks). One decision recorded with the plan's default: the placement rule per campaign from 50 clicks (Owner decisions).</t>
+          <t>Twelve choices, each with how it is checked or what is still open (Key choices tab); the owner decisions among them carry the plan's default and the alternative priced (Owner decisions).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Review 1</t>
+          <t>This workbook</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Seven corrections and seven smaller points applied (Review 1 fixes tab, with the acceptance checks). Three choices are recorded with the plan's default and the alternative priced (Owner decisions).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>This workbook</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Plan tabs first (Action list, Bulk upload — 130 rows that load — Needs console IDs — 39 rows —, T1–T4 and T3k keyword bids, stock, rank tracking, colour costs, monitoring, the SCS4 rules applied), then evidence tabs marked E. Every count is read from the same model as the document. Read-only analysis; nothing was changed in any tool.</t>
+          <t>Plan tabs first (Action list, Bulk upload — 130 rows that load — Needs console IDs — 39 rows —, T1–T4 and T3k keyword bids, stock, rank tracking, colour costs, monitoring, the key choices and the shared rules), then evidence tabs marked E. Every count is read from the same model as the document. Read-only analysis; nothing was changed in any tool.</t>
         </is>
       </c>
     </row>
@@ -790,305 +776,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Decisions the data cannot make</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>The numbers</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Options / note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Placement rule (review 2, the decision)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Plan default: top-of-search-first campaign by campaign wherever a placement has ≥50 clicks, the product average below that. On that rule 'cooling fitted sheet' keeps its rest-of-search modifier ($14.96 an order in rest of search vs $20.62 at top of search) and three campaigns price product pages on their own conversion.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Keep per campaign (default), or apply the rule product-wide (rest of search to 0% on all; family product-page rate).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Full Cool Grey cost (review 2)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The two Full raises wait for the $11.49 cost record to be checked against the supplier invoice: ceiling $1.38 at $11.49, $0.71 at $15.45.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Check the invoice; $11.49 → raises after the first conversion read; $15.45 → no raise, Full re-solved under the no-margin test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Spend level (review 1, decision 3)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Plan default: spend set by what a click earns; the envelope is an upper limit. That ends at $579/wk, 9.7% of last week's sales, leaving $137–256/wk of the envelope unused. Alternative priced: leave held bases unchanged → $690/wk (11.6%), Exact orders 204 instead of 181 a month — about 25 dollars for each extra order against $9.79 of contribution.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Confirm the ceiling rule (about 9.5% TACoS), or keep held bases and spend inside the envelope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>First held step (review 1, decision 1)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Plan default: the first step is the CPC paid, wave A (2) on 22 Oct and wave B (4) on 5 Nov; 90% steps follow a read. The earlier 90%-of-CPC first step could keep at most 45–84% of the clicks on the held rows (T3).</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Keep, or sign the 90% step on all held rows at once.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Loss-making colours (review 1, decision 2)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Plan default: hold Cal King Graphite, Queen Cool Blue, Queen Light Pink out of the spring order (798 units) until their cost records are checked. Queen Cool Blue and Light Pink are recorded at $16.00–16.20 against $12.40–12.48 on most Queen colours; at that cost and the $37.99 price they would earn $8.82 and $10.45 a unit. Cal King Graphite earns little because of fees. Full: 10 of 13 colours are recorded at about $15.45 (Colour costs).</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Fix the cost records first (then recompute and reorder), or hold them out as the plan does.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TACoS band</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Band 12.0% declared by this plan. Trailing 7 days 12.4% (1.03×).</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Confirm 12% or set another.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Rank-hold premium</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>$169/wk ($866 a month at September volume). Largest, by held term (campaign): 'cooling fitted sheet' (277390956383530) $258/month; 'cooling fitted sheet king' (43491018068645) $257/month; 'cooling fitted sheet queen' (202444515473718) $128/month; 'cooling king fitted sheet' (25820387388275) $43/month; 'king cooling fitted sheet' (22290954617594) $35/month</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Keep, or release named terms (they then step to their ceiling like any other row).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Rank trackers</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>10 untracked keywords with ≥5 September orders are held pending a rank (10 terms on 11 keyword rows ('cool fitted sheet king' sits in two campaigns)): 'cool fitted sheet queen', 'cooling fitted sheets king size', 'cool fitted sheet king', 'king size cooling fitted sheets', 'king size fitted sheets only cooling', 'king fitted sheets cooling', 'king size fitted sheets cooling', 'king size fitted sheet cool', 'queen cooling fitted sheet only', 'king size cooling fitted sheets only'</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Add them (and ideally all 36) to Data Dive and Command Center now, so 7-day medians exist before 22 Oct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shipments</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>1,884 units on August–October shipments show 'ready to ship' in Sellerboard; only the Full Light Grey and Cool Grey lines are being received.</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Confirm with the forwarder today that each has left, and its delivery appointment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Deal details</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>The 7 Oct Lightning Deal SKUs, deal price and committed units are in no source the plan can read.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Send them; the plan adds contribution at the deal price and the deal-day caps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Queen child</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Plan keeps Queen White; the audit pivots to Queen Graphite (129 sellable, its 168 inbound unconfirmed).</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Keep Queen White (back-up loaded), or take the pivot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Command Center budget doublings of 27 Sep</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Queen White campaign $25 → $50 and King campaign $20 → $40, made outside this plan.</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Keep as caps, or set back to $25 / $20 on 6 Oct before arming.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cal King and Twin</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Both pause for no margin; neither restarts by itself.</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Fix price, cost or fee tier before either is advertised or reordered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Satin Sponsored Brands on this product</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Three D-SF-SB campaigns for SATIN fitted sheets (and one paused Satin SB) sit under this product in Command Center.</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Re-map them; this plan does not touch them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>The first step at the CPC paid (on each held keyword's own price) and the 90% further steps, the 50-click placement line, the 85% wave B gate, the 30% guard, the ≥5-order pending-rank rule, the delivery cases, the 0.8 haircut, the 15/50-click blend, the 25%/30% step caps, the $0.50 floor, the $3.22 bound, the 12% band, the season, the 16 Oct FC-transfer date.</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Choices, not facts the data fixes.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:C18"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1282,7 +969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1555,7 +1242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2499,7 +2186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2940,7 +2627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7047,7 +6734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12978,7 +12665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17574,7 +17261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19981,7 +19668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21258,448 +20945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Review 1 (2 Oct): seven corrections and seven smaller points, and what this version does</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Every reviewer figure was re-checked against the workbook rows or live Sellerboard before it was applied. The right-hand column is the acceptance state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Found in the review</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>What this version does</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Acceptance</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>The first held price step sat below what the auctions clear at (90% of the CPC paid; at most 45–84% of clicks could survive it)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>First step = the CPC paid (lowest 100% of it); 90% steps only after a read. Wave A 2 campaigns on 22 Oct (one large Queen, one large King, two small), wave B 4 on 5 Nov. 10 held rows have under 5% headroom and hold. Forecast line with the first steps undone: no change (Budget &amp; envelope); the held saving ($585 a month) is the base cuts.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>T3, Budget &amp; envelope, Monitoring</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Held status decided on 17 of 53 Exact keywords</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Confirmed: 36 untracked keywords carry $1,985 and 136 orders; none is in Command Center, Data Dive or ASINsight. Held is now read per keyword; untracked keywords with ≥5 September orders are held pending a rank (11 keyword rows, 10 distinct terms, including 'cool fitted sheet king' in its own campaign). 4 riders above the ceiling priced by their own bid on 2 Oct. Keyword-level bids in T3k; the trackers are listed for the owner to add (Rank tracking).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>T3, T3k, Rank tracking</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OPEN until the trackers are added</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Premium list named the wrong keyword</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Every premium row is labelled by its held term and campaign ID (Owner decisions, document sections 3, 5b and 10).</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Owner decisions, T3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The 16 Oct arrivals are not confirmed</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Confirmed: Sellerboard shows 1,884 units 'ready to ship' and 15 being received. Tiers, triggers and run-outs now count only stock in hand, FC transfers and receiving lines; shipments count for reorders only. Stock &amp; reorder shows each line's status and units received; the E Checks line reads OPEN. King Beige: runs out about 13 Oct on hand; bids −50% now, ads pause 9 Oct.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder, E Checks</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OPEN until the forwarder confirms</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Two Twin campaigns left armed at $5.18 and $3.80</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Both pause on 2 Oct by the Cal King rule (product pages afford $0.24 under a $0.50 base floor); they do not restart by themselves.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bulk upload, T3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>"Loss-making colours" had no stated cause</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Colour costs tab: recorded cost, the size's usual cost, standard, current and realised price, and contribution three ways. Queen Cool Blue and Light Pink: cost records ($16.00–16.20 vs $12.48) and below-list selling; Cal King Graphite: fees. Queen Cool Blue's pace is marked clearance demand. Full: 10 of 13 colours are recorded at about $15.45 (the reviewer saw only the first inventory page); Full Cool Blue still earns less than Full Cool Grey at the standard price, so the move stands.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Colour costs, Stock &amp; reorder</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PASS (cost records: owner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>The plan ended near 8% TACoS against a 12–14% envelope</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Section 2 and the Summary state the rule: spend is set by what a click earns; the envelope is an upper limit. With the first held step at the CPC paid the plan now ends at $579/wk (9.7%). The alternative (held bases kept, $690/wk, 11.6%) is priced in Owner decisions.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Summary, Owner decisions, Budget &amp; envelope</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Owner decision recorded (default: ceiling rule)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Deal SKUs, price and units not in the pack</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>In no source the plan can read; asked of the owner (Owner decisions).</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Owner decisions</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>OPEN (owner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Which campaigns are expected to cap on 7 Oct</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Named in Monitoring (30-day budget use ≥50%): cool fitted sheet queen 79%; king cooling fitted sheet 58%; queen fitted sheet cooling 56%; cooling fitted sheet 52%; king size fitted sheets cooling 52%.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>A12: 'king size cooling fitted sheets only' said 'steps to its ceiling' but holds</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Notes rebuilt when the under-5% rule cancels a step; the row is now held pending rank and holds at $2.06 (CPC paid $2.03: no headroom).</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Empty values printed as text placeholders (E Checks, E Conflicts, E Push test by term)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Printed as a dash or "no term" throughout.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>E Checks, E Conflicts, E Push test by term</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cal King colours tiered "A – healthy" on negative contribution</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Tier capped: 'N – no margin' wherever contribution before ads is ≤ $0.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>E Inventory, T1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>One lever per write on 13 vs 15 campaigns</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>18 campaigns: 16 priced held or re-pointed, plus 2 re-pointed rows read in the console (child swap only).</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>E Checks, document section 2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S7</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Live budgets $450 vs $455</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Two figures, each labelled: $455/day on the 35 live Exact campaigns today (E Campaigns), $450/day after the 2 Oct pauses and revive, with the Auto.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Summary, Budget &amp; envelope</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:E17"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22093,7 +21339,394 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="130" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The key choices in this plan, and how each is checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Each choice is made from the data in this workbook; the right-hand column says how it is checked or what is still open. Owner decisions carry the plan's default (Owner decisions tab).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>What the plan does</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The first held price step</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>The first step on a held page-one term is the CPC paid itself, never under it: a step to 90% of the CPC paid on today's prices could keep at most 45–84% of the clicks. The step is checked on each held keyword's own price (bid × (1 + modifier)), not on the campaign base. Where a held keyword's bid sits under the base, a step on the campaign would take it under the CPC paid ('cooling fitted sheet queen' (202444515473718) bid $1.70 vs base $2.00: $4.11 → $3.36, 85% of the $3.95 CPC paid; 'cooling fitted sheet king' (43491018068645) bid $1.65 vs base $1.90: $3.63 → $3.07, 87% of the $3.54 CPC paid; 'king size fitted sheet cooling' (124359900887254) bid $0.75 vs base $1.90: $1.65 → $1.41, 39% of the $3.58 CPC paid; 'king size cooling fitted sheet' (22290954617594) bid $1.75 vs base $1.90: $3.50 → $2.89, 92% of the $3.14 CPC paid; 'king fitted sheet only cooling' (247354433604883) bid $1.90 vs base $2.61: $3.99 → $2.79, 73% of the $3.83 CPC paid; 'queen size fitted sheet only cooling' (659699120656) bid $1.50 vs base $1.60: $3.19 → $2.84, 94% of the $3.03 CPC paid), so those 6 campaigns keep their modifier and the held keyword's bid, and only riders step (2 of them have riders; in the other 4 every keyword is held and no top-of-search price moves). 'king size fitted sheet cooling' sits far under its campaign's CPC: its own clicks and CPC are read in the console before any step. Further steps (90% of the new CPC paid) only after a read.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>T3, T3k, Needs console IDs</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Lowest held keyword after a step: 100% of the CPC paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Two waves, and what the first step can cost</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Wave A (2 campaigns: 'cooling fitted sheet', 'cooling king fitted sheet') steps on 22 Oct, wave B (4) on 5 Nov. The CPC paid is an average, so a step to it can keep up to every click, not every click: for wave A (46 of 191 held orders) keeps every top-of-search click (the most it can keep): $743 and 40 orders a month; top-of-search clicks −25%: $586 and 32 orders a month; top-of-search clicks −50%: $429 and 24 orders a month. 5 Nov read, before wave B: wave B steps only if every wave A held keyword keeps at least 85% of its 6–19 Sep top-of-search impression share (keyword rows; 2–6 Oct where the keyword share is not reported) and its rank has not slipped more than 3 places. Between 70% and 85% the wave A step is kept but wave B waits one read (19 Nov); under 70% the wave A step is undone and wave B does not step this season.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Budget &amp; envelope, Monitoring, document 5b</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Cases and stop rule stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The guard</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The guard reads each held keyword's own top-of-search impression share (keyword rows of the targeting report) since the last write against 6–19 Sep, the 14 days before the Best Deal, leaving out 7–21 Oct; 70% or more keeps the walk going, under 70% undoes the last step. Where a keyword share is not reported, only periods after 2 Oct are compared (2–6 Oct for wave A, 22 Oct–4 Nov for wave B), so the keyword set is the same on both sides; then top-of-search clicks ÷ the season factor.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Needs console IDs, Monitoring</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>25 held keyword rows to read</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Held status, keyword by keyword</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Only 17 of 53 Exact keywords have a rank in any source; the other 36 carry $1,985 and 136 orders. A keyword is held when it ranks ≤20 on Command Center or Data Dive (7-day medians), or, with no tracker, took ≥5 orders in September (10 terms on 11 keyword rows ('cool fitted sheet king' sits in two campaigns), held pending a rank). 4 riders above the ceiling step by their own bid on 2 Oct.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T3, T3k, Rank tracking</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Open: the owner adds the trackers before 22 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Top of search first, campaign by campaign</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Exact top of search converts best on the product average, so it is held for rank and product pages and rest of search take the cuts. The comparison is made per campaign wherever a placement has 50 or more clicks, the product average only below that: 'cooling fitted sheet' keeps its 20% rest-of-search modifier ($14.96 an order there against $20.62 at top of search); the other rest-of-search cut stands. Product pages are priced on the campaign's own conversion from 50 clicks: 'cooling fitted sheet' 101 clicks, 10.89% → $1.17; 'cool fitted sheet queen' 93 clicks, 6.45% → $0.69; 'cool fitted sheet king' 59 clicks, 8.47% → $0.76.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>T2, T3, TOS-first</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Owner decision: per campaign (default) or product-wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The two Full raises</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>'full size cooling fitted sheet' at $1.18; 'cooling fitted sheet full size' at $0.53 would rise to the $1.38 ceiling on Full Cool Grey (tier A). That ceiling rests on an $11.49 cost record where 10 of 13 Full colours carry about $15.45; at $15.45 the unit earns $4.19, top of search affords $0.71 and product pages $0.28, under the $0.50 floor. Both raises wait for the cost to be checked against the supplier invoice: $11.49 confirmed → they start on the write after the first conversion read on Full Cool Grey; $15.45 → no raise, the Full ceiling is re-solved and the no-margin test re-run. No price rises before then.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T3, Owner decisions</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>No raise dated before the check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Stock: confirmed arrivals only</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tiers, triggers and run-outs count stock in hand, FC transfers (1,178) and the 15 units Amazon is receiving. The 1,884 units on August–October shipments Sellerboard shows 'ready to ship' count for reorders only until the forwarder confirms them; Stock &amp; reorder shows the confirmed run-out date beside the date if every shipment lands. Full White's 468 units are a planned PO due 25 Jan 2027, not a shipment.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stock &amp; reorder, E Checks</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Open: the forwarder confirms the shipments</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Twin and Cal King</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Paused on 2 Oct for no margin: product pages afford under half the $0.50 base floor (Twin $0.24). Neither restarts by itself when stock lands.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bulk upload, T3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Loss-making colours</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Colour costs tab: recorded cost, the size's usual cost, standard and realised price, and contribution three ways. Queen Cool Blue and Light Pink carry $16.00–16.20 against $12.48 on most Queen colours and sell below list; Cal King Graphite earns little because of fees; Queen Cool Blue's pace is clearance demand. These are held out of the spring order until their cost records are checked. Full Cool Blue earns less than Full Cool Grey at the standard price, so Full moves to Full Cool Grey.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Colour costs, Stock &amp; reorder</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Owner checks the cost records</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>What sets spend</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>What a click earns sets spend; the envelope (12–14% of trailing-7-day sales) is an upper limit, not a target. On that rule the plan ends at $579/wk (9.7%). Keeping the held bases instead costs $690/wk (11.6%); undoing the first held steps (base cuts kept) gives 181 orders at $579/wk.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Summary, Budget &amp; envelope, Owner decisions</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Owner decision: default is the ceiling rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The rank-hold premium</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>(CPC paid − ceiling) × forecast top-of-search clicks on every held row: $866 a month, $169/wk, each row labelled by its held term and campaign ID.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>T3, Owner decisions</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Every held row filled</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The 7 Oct Lightning Deal</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>SOP-32: writes on 2 Oct, arming 6 Oct, bids hold through the deal, no write 6–21 Oct, and those days leave every read. The campaigns expected to cap first are named in Monitoring. The deal SKUs, price and units are in no source the plan can read.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Monitoring, Owner decisions</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Open: the owner sends the deal details</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23195,7 +22828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23674,7 +23307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23929,7 +23562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30021,7 +29654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32064,7 +31697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33513,7 +33146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -33754,7 +33387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34391,7 +34024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40846,367 +40479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Review 2 (2 Oct): five corrections and six contradictions, and what this version does</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Every reviewer figure was recomputed from the model before it was applied; all hold. The right-hand column is the acceptance state.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Found in the review</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>What this version does</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Acceptance</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Six held keywords land below the CPC paid (step solved on the campaign base)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>The first step is checked on each held keyword's own price. 'cooling fitted sheet queen' (202444515473718) bid $1.70 vs base $2.00: $4.11 → $3.36, 85% of the $3.95 CPC paid; 'cooling fitted sheet king' (43491018068645) bid $1.65 vs base $1.90: $3.63 → $3.07, 87% of the $3.54 CPC paid; 'king size fitted sheet cooling' (124359900887254) bid $0.75 vs base $1.90: $1.65 → $1.41, 39% of the $3.58 CPC paid; 'king size cooling fitted sheet' (22290954617594) bid $1.75 vs base $1.90: $3.50 → $2.89, 92% of the $3.14 CPC paid; 'king fitted sheet only cooling' (247354433604883) bid $1.90 vs base $2.61: $3.99 → $2.79, 73% of the $3.83 CPC paid; 'queen size fitted sheet only cooling' (659699120656) bid $1.50 vs base $1.60: $3.19 → $2.84, 94% of the $3.03 CPC paid. Those 6 campaigns keep the modifier and the held keyword's bid; only riders step (2 have them; in the other 4 every keyword is held, so no top-of-search price moves). 'king size fitted sheet cooling': read its own clicks and CPC in the console before any step.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>T3, T3k, Needs console IDs</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Met: lowest held keyword after a step 100% of the CPC paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The guard read the campaign, not the held keyword</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>The guard reads each held keyword's own top-of-search impression share (keyword rows of the targeting report), 6–19 Sep and since the last write. 25 keyword rows replace the 16 campaign rows in Needs console IDs. Without a keyword share: periods after 2 Oct only (2–6 Oct for wave A, 22 Oct–4 Nov for wave B).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Needs console IDs, guard sentence</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Met: 25 keyword rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Top-of-search-first applied from the product average</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Per campaign wherever a placement has ≥50 clicks, the product average below that. 'cooling fitted sheet' (277390956383530) keeps its 20% rest-of-search modifier: $14.96 an order there vs $20.62 at top of search. Product pages on own conversion from 50 clicks: 'cooling fitted sheet' 101 clicks, 10.89% → $1.17; 'cool fitted sheet queen' 93 clicks, 6.45% → $0.69; 'cool fitted sheet king' 59 clicks, 8.47% → $0.76. Section 5c restated: top of search is held for rank, not because it is the cheapest order in every campaign.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>T2, T3, TOS-first, plan 5c</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Met; owner decision recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The two Full raises rest on a cost record the pack questions</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>'full size cooling fitted sheet' (69726426719654) at $1.18: raise path $1.38 held; 'cooling fitted sheet full size' (220584159657711) at $0.53: raise path $0.69, $0.90, $1.17, $1.38 held. Ceiling $1.38 at $11.49 ($8.15 a unit), $0.71 at $15.45 ($4.19; product pages $0.28, under the $0.50 floor). $11.49 confirmed → raises start on the write after the first conversion read on Full Cool Grey; $15.45 → no raise, ceiling re-solved, no-margin test re-run.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>T3, Owner decisions</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Met: no date before the check; both ceilings shown</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>The forecast treated the step to the CPC paid as free</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>The step can keep up to every click. Wave A (2 campaigns: 'cooling fitted sheet', 'cooling king fitted sheet'; 46 of 191 held orders): keeps every top-of-search click (the most it can keep) $743 / 40 orders a month; top-of-search clicks −25% $586 / 32 orders a month; top-of-search clicks −50% $429 / 24 orders a month. 5 Nov read, before wave B: wave B steps only if every wave A held keyword keeps at least 85% of its 6–19 Sep top-of-search impression share (keyword rows; 2–6 Oct where the keyword share is not reported) and its rank has not slipped more than 3 places. Between 70% and 85% the wave A step is kept but wave B waits one read (19 Nov); under 70% the wave A step is undone and wave B does not step this season.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Budget &amp; envelope, Monitoring, plan 5b</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Section 5 'no price goes up' vs two raises</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>No price rises: the Full raises are held for the cost check.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Plan 5, 5c, E Checks</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Run-outs counted unconfirmed shipments</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder, plan 6 and A16 show 'Runs out (confirmed stock)' beside 'Runs out (if every shipment lands)'.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>'First held steps undone' cell read 204 orders, $690/wk</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Corrected: undoing the first steps keeps the base cuts — 181 orders, $579/wk.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Budget &amp; envelope</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>10 vs 11 keywords held pending a rank</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>10 terms on 11 keyword rows ('cool fitted sheet king' sits in two campaigns), everywhere.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Summary, Owner decisions, E Checks</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Full White 468 units shown as 'ready to ship'</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Labelled as the planned PO due 25 Jan 2027.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Plan Table 3 printed '2 Oct ;'</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Every write printed with its action; modifier changes as percentages (T3 Write dates).</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Plan 5b, T3</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Met</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:E14"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -46922,7 +46195,460 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rules shared with the Cooling Sheets 4 Piece (SCS4) plan, and how this plan applies them</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Every rule is applied the same way as in SCS4_Final_Plan_20261001; the right-hand column gives this product's figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>What it says</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Here</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Posture</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Read on the trailing 7 days, not the month</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep–1 Oct: 12.4% (1.03×) → amber. September averaged 12.2%; the last full week 11.7%. Envelope $716–835/wk.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Summary, E Weekly posture</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Re-based child</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ceilings on the plan child, one family rate × 0.8 on re-pointed rows</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Full rows on Full Cool Grey ($8.15, Full uses the all-size rate 21.24% × 0.8: Full has 6 top-of-search clicks). King and Queen keep their own children, so their own clicks count (blend 15–50, own from 50).</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T1, T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>One lever per write</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Held and re-pointed campaigns change one thing per write, 14 days apart</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>18 campaigns. Held: price walk from 22 Oct, base after it. Re-pointed: child 2 Oct, levers from 22 Oct. Child and a price never on the same day (0).</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>T3 Write dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Placement shift (now TOS-first, owner 2 Oct)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>SCS4: no base cut to push clicks to top of search</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Product pages cost $22.34 an order vs $15.33 at top of search. Bases fall only where a product-page click costs more than it earns (28 rows).</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T2, T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>No-bid rows</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Rows with no readable bid are named, not counted as holds</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2 rows (both with no targets in the export) read in the console.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Needs console IDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Contribution basis</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Realised margin before ads, same window; Sep ≥20 units, else 15 Jul–Sep, else Apr–Sep</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Queen White $10.74, King White $8.98, Full Cool Grey $8.15. The audit's 31.3% ($12.13) and Command Center's 21.5% ($7.19) are not used.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>T1, E Conflicts</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delivery-aware forecast</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Best / central / worst; clicks fall with (price ÷ CPC) below the CPC paid</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Central 31 Dec: Exact orders 224 → 181 (range 171–192). The worst case loses fewer held orders than the central one because the guard stops the walk earlier there.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Budget &amp; envelope, T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Freezes</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Rank fell &gt;10 places in 30 days: every lever frozen</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>No freezes. The audit's 'cooling fitted sheet king 18 (was 1)' is a single-day read; the 7-day medians are CC 2 and DD 2.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>E Rank sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>One stock clock</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Tiers, triggers, run-outs and reorders on one seasonal pace</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Season Oct 0.59, Nov 0.61, Dec 0.5, Jan 0.38, Feb 0.57, Mar 1.15, Apr 1.3, May 1.21 of Q3; dated arrivals per SKU.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stock &amp; reorder, E Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Held lookup</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Every live keyword, either rank source</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>16 held; 14 multi-keyword campaigns read keyword by keyword.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Spring order</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sized to 31 May, placed by 1 Dec or the 90-day reorder date</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>4,988 units (1,956 needed to reach 31 Mar).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stock &amp; reorder</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bases staged</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Repeat until within 5% of what a product-page click affords</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>17 bases take more than one dated step; held bases stop at the total-order guard (1).</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>One baseline, cumulative; impression share, not raw clicks</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Held-term guard, read on the held keyword: before each write, compare the held keyword's own top-of-search impression share since the last write (keyword rows of the targeting report; leaving out 7–21 Oct, the Lightning Deal and its 14-day settle) with its share in 6–19 Sep, the last 14 days before the 20–30 Sep Best Deal; write the next price step only while the share stays at 70% or more of that pre-plan level, and undo the last step (end the walk) if it has fallen below 70% or the rank slipped more than 3 places (15% above rank 20). Where a keyword-level share is not reported, compare periods after 2 Oct only (2–6 Oct for wave A, 22 Oct–4 Nov for wave B), so the keyword set is the same on both sides; then top-of-search clicks divided by the season factor.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>T3 header, Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Held losses</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Held terms must not lose more than the rest</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Held lose 28 of 191 (15%; 5 from the first price step), not held 12 of 24 (48%).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Budget &amp; envelope</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>(CPC paid − ceiling) × forecast top-of-search clicks, every held row</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>$866 a month = $169/wk at last week's volume (0.8366 of September).</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>T3, Owner decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Held steps (differs here)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>SCS4: each held step at least 90% of the CPC paid</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Here the first step is the CPC paid itself (lowest 100% of it); 90% steps follow only after a read, because a 90% step on today's prices could keep at most 45–84% of the clicks (T3). No −15% incrementality step on held terms.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Back-up ads</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Loaded paused in the bulk file</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>32 product-ad creates (King Cool Grey, Queen Graphite, Full Light Grey).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bulk upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Deal (new for this product)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SOP-32 for a Lightning Deal</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>No write 6–21 Oct; bids hold through 7 Oct; the 7–21 Oct days leave every read; new campaigns not before 22 Oct.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Monitoring, Action list</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -54508,7 +54234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -54768,7 +54494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57909,7 +57635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -60078,7 +59804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -61727,7 +61453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -61946,7 +61672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62771,7 +62497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -63023,7 +62749,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -63874,460 +63600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The rules the SCS4 pack ended with after three reviews, and how this plan applies them</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Every rule is applied the same way as in SCS4_Final_Plan_20261001; the right-hand column gives this product's figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>What it says</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Here</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Posture</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Read on the trailing 7 days, not the month</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>25 Sep–1 Oct: 12.4% (1.03×) → amber. September averaged 12.2%; the last full week 11.7%. Envelope $716–835/wk.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Summary, E Weekly posture</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Re-based child</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Ceilings on the plan child, one family rate × 0.8 on re-pointed rows</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Full rows on Full Cool Grey ($8.15, Full uses the all-size rate 21.24% × 0.8: Full has 6 top-of-search clicks). King and Queen keep their own children, so their own clicks count (blend 15–50, own from 50).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>T1, T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>One lever per write</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Held and re-pointed campaigns change one thing per write, 14 days apart</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>18 campaigns. Held: price walk from 22 Oct, base after it. Re-pointed: child 2 Oct, levers from 22 Oct. Child and a price never on the same day (0).</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>T3 Write dates</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Placement shift (now TOS-first, owner 2 Oct)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>SCS4: no base cut to push clicks to top of search</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Product pages cost $22.34 an order vs $15.33 at top of search. Bases fall only where a product-page click costs more than it earns (28 rows).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>T2, T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>No-bid rows</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Rows with no readable bid are named, not counted as holds</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2 rows (both with no targets in the export) read in the console.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Needs console IDs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Contribution basis</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Realised margin before ads, same window; Sep ≥20 units, else 15 Jul–Sep, else Apr–Sep</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Queen White $10.74, King White $8.98, Full Cool Grey $8.15. The audit's 31.3% ($12.13) and Command Center's 21.5% ($7.19) are not used.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>T1, E Conflicts</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Delivery-aware forecast</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Best / central / worst; clicks fall with (price ÷ CPC) below the CPC paid</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Central 31 Dec: Exact orders 224 → 181 (range 171–192). The worst case loses fewer held orders than the central one because the guard stops the walk earlier there.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Budget &amp; envelope, T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Freezes</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Rank fell &gt;10 places in 30 days: every lever frozen</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>No freezes. The audit's 'cooling fitted sheet king 18 (was 1)' is a single-day read; the 7-day medians are CC 2 and DD 2.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>E Rank sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>One stock clock</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Tiers, triggers, run-outs and reorders on one seasonal pace</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Season Oct 0.59, Nov 0.61, Dec 0.5, Jan 0.38, Feb 0.57, Mar 1.15, Apr 1.3, May 1.21 of Q3; dated arrivals per SKU.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder, E Inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Held lookup</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Every live keyword, either rank source</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>16 held; 14 multi-keyword campaigns read keyword by keyword.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Spring order</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Sized to 31 May, placed by 1 Dec or the 90-day reorder date</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>4,988 units (1,956 needed to reach 31 Mar).</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Bases staged</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Repeat until within 5% of what a product-page click affords</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>17 bases take more than one dated step; held bases stop at the total-order guard (1).</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>One baseline, cumulative; impression share, not raw clicks</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Held-term guard, read on the held keyword: before each write, compare the held keyword's own top-of-search impression share since the last write (keyword rows of the targeting report; leaving out 7–21 Oct, the Lightning Deal and its 14-day settle) with its share in 6–19 Sep, the last 14 days before the 20–30 Sep Best Deal; write the next price step only while the share stays at 70% or more of that pre-plan level, and undo the last step (end the walk) if it has fallen below 70% or the rank slipped more than 3 places (15% above rank 20). Where a keyword-level share is not reported, compare periods after 2 Oct only (2–6 Oct for wave A, 22 Oct–4 Nov for wave B), so the keyword set is the same on both sides; then top-of-search clicks divided by the season factor.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>T3 header, Monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Held losses</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Held terms must not lose more than the rest</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Held lose 28 of 191 (15%; 5 from the first price step), not held 12 of 24 (48%).</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Budget &amp; envelope</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>(CPC paid − ceiling) × forecast top-of-search clicks, every held row</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>$866 a month = $169/wk at last week's volume (0.8366 of September).</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>T3, Owner decisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Held steps (changed by review 1)</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>SCS4: each held step at least 90% of the CPC paid</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Here the first step is the CPC paid itself (lowest 100% of it); 90% steps follow only after a read, because a 90% step on today's prices could keep at most 45–84% of the clicks (T3). No −15% incrementality step on held terms.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Back-up ads</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Loaded paused in the bulk file</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>32 product-ad creates (King Cool Grey, Queen Graphite, Full Light Grey).</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bulk upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Deal (new for this product)</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>SOP-32 for a Lightning Deal</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>No write 6–21 Oct; bids hold through 7 Oct; the 7–21 Oct days leave every read; new campaigns not before 22 Oct.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Monitoring, Action list</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:D21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -64605,1069 +63878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Exact placements — totals (30 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Command Center, measured per campaign; off-Amazon folded into rest of search.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Placement</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Spend $</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Orders</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>CPC $</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CVR %</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Cost per order $</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Share of clicks %</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Share of spend %</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Top of search</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2575.74</v>
-      </c>
-      <c r="C4" t="n">
-        <v>791</v>
-      </c>
-      <c r="D4" t="n">
-        <v>168</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="F4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="H4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I4" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Product pages</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>737.22</v>
-      </c>
-      <c r="C5" t="n">
-        <v>396</v>
-      </c>
-      <c r="D5" t="n">
-        <v>33</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>22.34</v>
-      </c>
-      <c r="H5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rest of search</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>405.45</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1125</v>
-      </c>
-      <c r="D6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="H6" t="n">
-        <v>49</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:I6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Aged stock (Command Center LTSF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Workflow 24 is at risk; no clearance pricing is proposed here (the season, not age, is the issue).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Measure</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aged units</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Monthly surcharge now $</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>210.77</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Six-month horizon $</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sellerboard Sep long-term storage fee $</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>229.11</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:B7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Where the sources disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Where used</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Audit single read (29 Sep) vs Command Center and Data Dive 7-day medians</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>'cooling fitted sheet king' audit 18 vs CC 2 / DD 2; 'cooling king size fitted sheets' audit 21 vs CC 6.5 / DD —</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ranks: 7-day medians</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Queen White stock</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Audit (61 available, 29 Sep) vs Sellerboard (2 Oct)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>110 sellable + 151 FC transfer</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sellerboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Arrival dates</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Audit 'dated and confirmed' arrivals vs Sellerboard shipment status (2 Oct)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Audit: 16 Oct for King and Queen, 5 Nov for Twin. Sellerboard: 1,884 units on August–October lines 'ready to ship', 15 being received; FC transfers carry no date</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tiers and triggers on confirmed stock; shipments for reorders only</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Audit 31.3% ($12.13) · Command Center 21.5% ($7.19, King White $8.19) · Sellerboard realised</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sellerboard September $9.79 a unit across the product; per child in T1 (King White $8.98, Queen White $10.74)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sellerboard, per child</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Market bound</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Audit own CPC + 15% ($3.72–3.78) vs the account stand-in</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>$3.22 (account-wide $2.80 + 15%)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>$3.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Season</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Own last year (launch, no ads to February) vs the category</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Oct–Feb: the higher of the category shape and our own pre-ads month; Mar–Sep: our own months</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stock &amp; reorder</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ad orders</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Command Center attributed vs Sellerboard same-SKU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Same-SKU share 25.2% of ad sales (Sellerboard September)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>E Financials</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Campaign mapping</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Command Center product 44 includes Satin Sponsored Brands</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>D-SF-SB campaigns advertise satin fitted sheets</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Out of scope</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:D11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cross-checks (run on the same model the document is written from)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sellerboard per-SKU units = family total, 1 Apr–30 Sep</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7,307 = 7,307 (dashboard)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Exact spend = plan rows (Command Center, 30 days)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>$3,718.41 on 38 rows ($3,585 on the 35 live); + Auto $82.56 = all campaigns</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Audit decisions reconciled</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>116 of 116: MODIFY 57, AGREE 37, REJECT 15, HOLD 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>No top-of-search price above its ceiling; rises only to the ceiling on tier-A children (TOS-first)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0 raises, all to the ceiling on tier-A Full Cool Grey; 0 past a ceiling; 0 on a child below tier A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOS-first: top of search gains share of Exact spend and orders</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>top of search 36.3% → 43.9% of clicks, 69.8% → 84.9% of spend, 76.3% → 87.5% of orders (central, 31 Dec)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>No bid rises anywhere</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0 keyword bids raised in the bulk file (revive bases are set, not raised); the $0.50 floor only stops a cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Non-held price paths end within 5% of their ceiling; held paths end where the guard stops them</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>non-held: worst end 1.8% above the ceiling; held: 14 end above it by design, priced in the rank-hold premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>First held step at the CPC paid on every held keyword's own price (review 2)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>lowest held keyword after a first step 100% of the campaign's top-of-search CPC paid; 6 held keywords whose bid sits under the campaign base would land under it, so their 6 campaigns keep the modifier and step the riders only; further steps (90% of the new CPC paid) only after a read</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Guard read per held keyword (review 2)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>25 held keyword rows in Needs console IDs (keyword top-of-search impression share 6–19 Sep), none per campaign</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Placement rule per campaign from 50 clicks (review 2)</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rest-of-search modifier kept on 1 campaign(s) where rest of search is the cheaper order on its own ≥50 clicks ('cooling fitted sheet' $14.96 vs $20.62 at top of search); 1 cut on the product rate (under 50 rest-of-search clicks)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Product-page ceiling on own conversion from 50 clicks (review 2)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>'cooling fitted sheet' 101 clicks, 10.89% → $1.17; 'cool fitted sheet queen' 93 clicks, 6.45% → $0.69; 'cool fitted sheet king' 59 clicks, 8.47% → $0.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Full raises held for the cost check (review 2)</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>'full size cooling fitted sheet' $1.18: ceiling $1.38 at $11.49, $0.71 at $15.45; 'cooling fitted sheet full size' $0.53: ceiling $1.38 at $11.49, $0.71 at $15.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Wave A forecast cases and the wave B stop rule (review 2)</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>wave A (2 campaigns, 46 of 191 held orders): keeps every top-of-search click (the most it can keep): $743 / 40 orders a month; top-of-search clicks −25%: $586 / 32 orders a month; top-of-search clicks −50%: $429 / 24 orders a month</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Deal window (SOP-32): no write on any campaign 6–21 Oct</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0 writes dated 6–21 Oct; held first steps 22 Oct and 5 Nov; bids hold through the 7 Oct Lightning Deal</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Rank-hold premium on the ceiling rate</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(CPC paid − ceiling) × forecast top-of-search clicks on all 16 held rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>One lever per write on held and re-pointed campaigns</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>18 campaigns (16 priced, 2 read in the console with a child swap only); child and a price on the same day: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Held rollout split across two dates (review 1)</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>wave A 2 campaigns on 22 Oct, wave B 4 on 5 Nov</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Held test per keyword (review 1)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>17 of 53 Exact keywords have a rank; untracked keywords with ≥5 September orders are held pending rank (10 terms on 11 keyword rows; 'cool fitted sheet king' sits in two campaigns); 4 riders above the ceiling are priced by their own bid on 2 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Rank coverage (review 1)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>11 untracked keywords with ≥5 September orders need a tracker before 22 Oct (Rank tracking tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Twin at the Cal King rule (review 1)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2 Twin Exacts paused on 2 Oct (product pages afford $0.24 under a $0.50 floor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Held status read on every live keyword, either rank source (7-day medians)</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>16 held campaigns (0 on Data Dive alone); 14 live multi-keyword campaigns read keyword by keyword</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Audit single-day ranks checked against 7-day medians</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2 terms where the audit's 29 Sep read differs: 'cooling fitted sheet king' audit 18 vs CC 2 / DD 2; 'cooling king size fitted sheets' audit 21 vs CC 6.5 / DD — — no rank collapse once read on 7 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Non-held bases end within 5% of what a product-page click affords; held bases stop where the order guard binds</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0 stop at the $0.50 floor; 17 take more than one dated step; held: 1 stop at the order guard</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>One stock clock; tiers and triggers on confirmed stock only</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>tiers, triggers and run-out dates use stock in hand, FC transfers and lines Amazon is receiving; 1,884 units on 'ready to ship' shipments count for reorders only (5 children would move up a tier if they land)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Held terms keep more of their delivery than the rest (central)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>held lose 28.4 of 191, non-held 11.5 of 24</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Rows priced on the plan child</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>contribution from the plan child for every row (Full on Full Cool Grey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>No row advertises a child that loses money before ads</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Full off Full Cool Blue; Cal King paused</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Spend envelope</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>central: $697/wk after 2 Oct, $607 at 5 Nov, $579 at 31 Dec vs envelope $716–835 (12–14% of the trailing 7 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Shipments: units reconcile; arrival not confirmed</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1,899 units on shipment lines = Sellerboard 'sent to FBA'; only 15 are being received; the rest are 'ready to ship' (August–October): confirm with the forwarder</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FC transfers dated</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1178 units in FC transfer counted from 16 Oct (the audit's dated arrival); confirm in Seller Central</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Top-of-search impression share (guard metric)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>not in any export: all 16 held campaigns read it in the console before 22 Oct (Needs console IDs)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:C34"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -76128,7 +74339,1069 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exact placements — totals (30 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Command Center, measured per campaign; off-Amazon folded into rest of search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Spend $</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>CPC $</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>CVR %</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Cost per order $</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Share of clicks %</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Share of spend %</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Top of search</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2575.74</v>
+      </c>
+      <c r="C4" t="n">
+        <v>791</v>
+      </c>
+      <c r="D4" t="n">
+        <v>168</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Product pages</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>737.22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>396</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rest of search</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>405.45</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="H6" t="n">
+        <v>49</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:I6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Aged stock (Command Center LTSF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Workflow 24 is at risk; no clearance pricing is proposed here (the season, not age, is the issue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aged units</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Monthly surcharge now $</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>210.77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Six-month horizon $</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sellerboard Sep long-term storage fee $</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>229.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Where the sources disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Where used</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Audit single read (29 Sep) vs Command Center and Data Dive 7-day medians</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'cooling fitted sheet king' audit 18 vs CC 2 / DD 2; 'cooling king size fitted sheets' audit 21 vs CC 6.5 / DD —</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ranks: 7-day medians</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Queen White stock</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Audit (61 available, 29 Sep) vs Sellerboard (2 Oct)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>110 sellable + 151 FC transfer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sellerboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Arrival dates</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Audit 'dated and confirmed' arrivals vs Sellerboard shipment status (2 Oct)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Audit: 16 Oct for King and Queen, 5 Nov for Twin. Sellerboard: 1,884 units on August–October lines 'ready to ship', 15 being received; FC transfers carry no date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tiers and triggers on confirmed stock; shipments for reorders only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Audit 31.3% ($12.13) · Command Center 21.5% ($7.19, King White $8.19) · Sellerboard realised</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sellerboard September $9.79 a unit across the product; per child in T1 (King White $8.98, Queen White $10.74)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sellerboard, per child</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Market bound</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Audit own CPC + 15% ($3.72–3.78) vs the account stand-in</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>$3.22 (account-wide $2.80 + 15%)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>$3.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Season</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Own last year (launch, no ads to February) vs the category</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oct–Feb: the higher of the category shape and our own pre-ads month; Mar–Sep: our own months</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stock &amp; reorder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ad orders</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Command Center attributed vs Sellerboard same-SKU</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Same-SKU share 25.2% of ad sales (Sellerboard September)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>E Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campaign mapping</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Command Center product 44 includes Satin Sponsored Brands</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D-SF-SB campaigns advertise satin fitted sheets</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:D11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cross-checks (run on the same model the document is written from)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sellerboard per-SKU units = family total, 1 Apr–30 Sep</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,307 = 7,307 (dashboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Exact spend = plan rows (Command Center, 30 days)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>$3,718.41 on 38 rows ($3,585 on the 35 live); + Auto $82.56 = all campaigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Audit decisions reconciled</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>116 of 116: MODIFY 57, AGREE 37, REJECT 15, HOLD 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>No top-of-search price above its ceiling; rises only to the ceiling on tier-A children (TOS-first)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0 raises, all to the ceiling on tier-A Full Cool Grey; 0 past a ceiling; 0 on a child below tier A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOS-first: top of search gains share of Exact spend and orders</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>top of search 36.3% → 43.9% of clicks, 69.8% → 84.9% of spend, 76.3% → 87.5% of orders (central, 31 Dec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>No bid rises anywhere</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0 keyword bids raised in the bulk file (revive bases are set, not raised); the $0.50 floor only stops a cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Non-held price paths end within 5% of their ceiling; held paths end where the guard stops them</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>non-held: worst end 1.8% above the ceiling; held: 14 end above it by design, priced in the rank-hold premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>First held step at the CPC paid on every held keyword's own price</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lowest held keyword after a first step 100% of the campaign's top-of-search CPC paid; 6 held keywords whose bid sits under the campaign base would land under it, so their 6 campaigns keep the modifier and step the riders only; further steps (90% of the new CPC paid) only after a read</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Guard read per held keyword</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25 held keyword rows in Needs console IDs (keyword top-of-search impression share 6–19 Sep), none per campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Placement rule per campaign from 50 clicks</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rest-of-search modifier kept on 1 campaign(s) where rest of search is the cheaper order on its own ≥50 clicks ('cooling fitted sheet' $14.96 vs $20.62 at top of search); 1 cut on the product rate (under 50 rest-of-search clicks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Product-page ceiling on own conversion from 50 clicks</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'cooling fitted sheet' 101 clicks, 10.89% → $1.17; 'cool fitted sheet queen' 93 clicks, 6.45% → $0.69; 'cool fitted sheet king' 59 clicks, 8.47% → $0.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Full raises held for the cost check</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'full size cooling fitted sheet' $1.18: ceiling $1.38 at $11.49, $0.71 at $15.45; 'cooling fitted sheet full size' $0.53: ceiling $1.38 at $11.49, $0.71 at $15.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Wave A forecast cases and the wave B stop rule</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>wave A (2 campaigns, 46 of 191 held orders): keeps every top-of-search click (the most it can keep): $743 / 40 orders a month; top-of-search clicks −25%: $586 / 32 orders a month; top-of-search clicks −50%: $429 / 24 orders a month</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Deal window (SOP-32): no write on any campaign 6–21 Oct</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0 writes dated 6–21 Oct; held first steps 22 Oct and 5 Nov; bids hold through the 7 Oct Lightning Deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Rank-hold premium on the ceiling rate</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>(CPC paid − ceiling) × forecast top-of-search clicks on all 16 held rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>One lever per write on held and re-pointed campaigns</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18 campaigns (16 priced, 2 read in the console with a child swap only); child and a price on the same day: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Held rollout split across two dates</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wave A 2 campaigns on 22 Oct, wave B 4 on 5 Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Held test per keyword</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>17 of 53 Exact keywords have a rank; untracked keywords with ≥5 September orders are held pending rank (10 terms on 11 keyword rows; 'cool fitted sheet king' sits in two campaigns); 4 riders above the ceiling are priced by their own bid on 2 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rank coverage</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11 untracked keywords with ≥5 September orders need a tracker before 22 Oct (Rank tracking tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Twin at the Cal King rule</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2 Twin Exacts paused on 2 Oct (product pages afford $0.24 under a $0.50 floor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Held status read on every live keyword, either rank source (7-day medians)</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16 held campaigns (0 on Data Dive alone); 14 live multi-keyword campaigns read keyword by keyword</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Audit single-day ranks checked against 7-day medians</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2 terms where the audit's 29 Sep read differs: 'cooling fitted sheet king' audit 18 vs CC 2 / DD 2; 'cooling king size fitted sheets' audit 21 vs CC 6.5 / DD — — no rank collapse once read on 7 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non-held bases end within 5% of what a product-page click affords; held bases stop where the order guard binds</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0 stop at the $0.50 floor; 17 take more than one dated step; held: 1 stop at the order guard</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>One stock clock; tiers and triggers on confirmed stock only</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>tiers, triggers and run-out dates use stock in hand, FC transfers and lines Amazon is receiving; 1,884 units on 'ready to ship' shipments count for reorders only (5 children would move up a tier if they land)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Held terms keep more of their delivery than the rest (central)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>held lose 28.4 of 191, non-held 11.5 of 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rows priced on the plan child</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>contribution from the plan child for every row (Full on Full Cool Grey)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>No row advertises a child that loses money before ads</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Full off Full Cool Blue; Cal King paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Spend envelope</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>central: $697/wk after 2 Oct, $607 at 5 Nov, $579 at 31 Dec vs envelope $716–835 (12–14% of the trailing 7 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shipments: units reconcile; arrival not confirmed</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1,899 units on shipment lines = Sellerboard 'sent to FBA'; only 15 are being received; the rest are 'ready to ship' (August–October): confirm with the forwarder</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FC transfers dated</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1178 units in FC transfer counted from 16 Oct (the audit's dated arrival); confirm in Seller Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Top-of-search impression share (guard metric)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>not in any export: all 16 held campaigns read it in the console before 22 Oct (Needs console IDs)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:C34"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -79327,7 +78600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -79588,7 +78861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -81417,7 +80690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -83101,4 +82374,303 @@
   <autoFilter ref="A3:F62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decisions the data cannot make</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>The numbers</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Options / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Placement rule</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Plan default: top-of-search-first campaign by campaign wherever a placement has ≥50 clicks, the product average below that. On that rule 'cooling fitted sheet' keeps its rest-of-search modifier ($14.96 an order in rest of search vs $20.62 at top of search) and three campaigns price product pages on their own conversion.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Keep per campaign (default), or apply the rule product-wide (rest of search to 0% on all; family product-page rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Full Cool Grey cost</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>The two Full raises wait for the $11.49 cost record to be checked against the supplier invoice: ceiling $1.38 at $11.49, $0.71 at $15.45.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Check the invoice; $11.49 → raises after the first conversion read; $15.45 → no raise, Full re-solved under the no-margin test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Spend level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Plan default: spend set by what a click earns; the envelope is an upper limit. That ends at $579/wk, 9.7% of last week's sales, leaving $137–256/wk of the envelope unused. Alternative priced: leave held bases unchanged → $690/wk (11.6%), Exact orders 204 instead of 181 a month — about 25 dollars for each extra order against $9.79 of contribution.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Confirm the ceiling rule (about 9.5% TACoS), or keep held bases and spend inside the envelope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>First held step</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Plan default: the first step is the CPC paid, wave A (2) on 22 Oct and wave B (4) on 5 Nov; 90% steps follow a read. The earlier 90%-of-CPC first step could keep at most 45–84% of the clicks on the held rows (T3).</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Keep, or sign the 90% step on all held rows at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Loss-making colours</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Plan default: hold Cal King Graphite, Queen Cool Blue, Queen Light Pink out of the spring order (798 units) until their cost records are checked. Queen Cool Blue and Light Pink are recorded at $16.00–16.20 against $12.40–12.48 on most Queen colours; at that cost and the $37.99 price they would earn $8.82 and $10.45 a unit. Cal King Graphite earns little because of fees. Full: 10 of 13 colours are recorded at about $15.45 (Colour costs).</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Fix the cost records first (then recompute and reorder), or hold them out as the plan does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TACoS band</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Band 12.0% declared by this plan. Trailing 7 days 12.4% (1.03×).</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Confirm 12% or set another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rank-hold premium</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>$169/wk ($866 a month at September volume). Largest, by held term (campaign): 'cooling fitted sheet' (277390956383530) $258/month; 'cooling fitted sheet king' (43491018068645) $257/month; 'cooling fitted sheet queen' (202444515473718) $128/month; 'cooling king fitted sheet' (25820387388275) $43/month; 'king cooling fitted sheet' (22290954617594) $35/month</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Keep, or release named terms (they then step to their ceiling like any other row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rank trackers</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>10 untracked keywords with ≥5 September orders are held pending a rank (10 terms on 11 keyword rows ('cool fitted sheet king' sits in two campaigns)): 'cool fitted sheet queen', 'cooling fitted sheets king size', 'cool fitted sheet king', 'king size cooling fitted sheets', 'king size fitted sheets only cooling', 'king fitted sheets cooling', 'king size fitted sheets cooling', 'king size fitted sheet cool', 'queen cooling fitted sheet only', 'king size cooling fitted sheets only'</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Add them (and ideally all 36) to Data Dive and Command Center now, so 7-day medians exist before 22 Oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shipments</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>1,884 units on August–October shipments show 'ready to ship' in Sellerboard; only the Full Light Grey and Cool Grey lines are being received.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Confirm with the forwarder today that each has left, and its delivery appointment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Deal details</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>The 7 Oct Lightning Deal SKUs, deal price and committed units are in no source the plan can read.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Send them; the plan adds contribution at the deal price and the deal-day caps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Queen child</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Plan keeps Queen White; the audit pivots to Queen Graphite (129 sellable, its 168 inbound unconfirmed).</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Keep Queen White (back-up loaded), or take the pivot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Command Center budget doublings of 27 Sep</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Queen White campaign $25 → $50 and King campaign $20 → $40, made outside this plan.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Keep as caps, or set back to $25 / $20 on 6 Oct before arming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cal King and Twin</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Both pause for no margin; neither restarts by itself.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Fix price, cost or fee tier before either is advertised or reordered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Satin Sponsored Brands on this product</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Three D-SF-SB campaigns for SATIN fitted sheets (and one paused Satin SB) sit under this product in Command Center.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Re-map them; this plan does not touch them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>The first step at the CPC paid (on each held keyword's own price) and the 90% further steps, the 50-click placement line, the 85% wave B gate, the 30% guard, the ≥5-order pending-rank rule, the delivery cases, the 0.8 haircut, the 15/50-click blend, the 25%/30% step caps, the $0.50 floor, the $3.22 bound, the 12% band, the season, the 16 Oct FC-transfer date.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Choices, not facts the data fixes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:C18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>